--- a/results/log_pv_cap_per_inst/log_pv_cap_per_inst_densities_fdensity_tests.xlsx
+++ b/results/log_pv_cap_per_inst/log_pv_cap_per_inst_densities_fdensity_tests.xlsx
@@ -451,27 +451,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>81.46***</t>
+          <t>83.78***</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.08***</t>
+          <t>13.02***</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6701.39***</t>
+          <t>7188.68***</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>43.62***</t>
+          <t>80.42***</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>27.87***</t>
+          <t>85.03***</t>
         </is>
       </c>
     </row>
@@ -483,27 +483,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>81.46***</t>
+          <t>83.78***</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.81***</t>
+          <t>4.37***</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6650.67***</t>
+          <t>7038.26***</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.44***</t>
+          <t>19.88***</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>27.87***</t>
+          <t>85.03***</t>
         </is>
       </c>
     </row>
@@ -515,27 +515,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>81.46***</t>
+          <t>83.78***</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.22***</t>
+          <t>4.61***</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6653.91***</t>
+          <t>7040.41***</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8.49***</t>
+          <t>14.30***</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>27.87***</t>
+          <t>85.03***</t>
         </is>
       </c>
     </row>
